--- a/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
   <si>
     <t>Mat</t>
   </si>
@@ -88,13 +88,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>LEON</t>
+    <t>LICEA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
   </si>
   <si>
     <t>ALVAREZ</t>
@@ -106,34 +121,25 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>LICEA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>TEHUINTLE</t>
-  </si>
-  <si>
     <t>TAPIA</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>NARVAEZ</t>
+    <t>SORIANO</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>MORAN</t>
@@ -145,31 +151,28 @@
     <t>CELICEO</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TLEHUACTLE</t>
+    <t>JESUS</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
+  </si>
+  <si>
+    <t>IVAN</t>
   </si>
   <si>
     <t>AYELEN</t>
   </si>
   <si>
-    <t>MARLENE ALICIA</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
+    <t>QADMIEL TAMARA</t>
+  </si>
+  <si>
+    <t>ADRIANA</t>
+  </si>
+  <si>
+    <t>ROMARIO ALDAIR</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -181,28 +184,7 @@
     <t>PAOLA</t>
   </si>
   <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>NURIEL</t>
-  </si>
-  <si>
-    <t>DANIELA</t>
-  </si>
-  <si>
-    <t>CRISTINA</t>
-  </si>
-  <si>
     <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
-    <t>ARIEL</t>
   </si>
 </sst>
 </file>
@@ -603,19 +585,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -629,19 +611,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,10 +637,10 @@
         <v>35</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>5</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -667,7 +649,7 @@
         <v>85.70999999999999</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -681,10 +663,10 @@
         <v>26</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>7</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>19</v>
@@ -693,7 +675,7 @@
         <v>73.08</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -707,19 +689,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>78.26000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -733,10 +715,10 @@
         <v>32</v>
       </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>11</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
       </c>
       <c r="F7">
         <v>21</v>
@@ -745,7 +727,7 @@
         <v>65.63</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -759,19 +741,19 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G8">
-        <v>88.23999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -824,16 +806,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
         <v>29</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>85.29000000000001</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -847,16 +832,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>73.68000000000001</v>
+      </c>
+      <c r="H3">
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,16 +858,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
         <v>30</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -893,16 +884,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
+        <v>7</v>
+      </c>
+      <c r="F5">
         <v>19</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>73.08</v>
+      </c>
+      <c r="H5">
+        <v>6.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -916,16 +910,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H6">
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -939,16 +936,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>68.75</v>
+      </c>
+      <c r="H7">
+        <v>6.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -962,16 +962,19 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>97.06</v>
+      </c>
+      <c r="H8">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1024,19 +1027,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>94.12</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1050,19 +1053,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>71.05</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1076,10 +1079,10 @@
         <v>35</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>5</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>30</v>
@@ -1102,10 +1105,10 @@
         <v>26</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>7</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>19</v>
@@ -1114,7 +1117,7 @@
         <v>73.08</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1128,19 +1131,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>78.26000000000001</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1154,19 +1157,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7">
-        <v>65.63</v>
+        <v>68.75</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1180,16 +1183,16 @@
         <v>34</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8">
-        <v>88.23999999999999</v>
+        <v>97.06</v>
       </c>
       <c r="H8">
         <v>8</v>
@@ -1202,7 +1205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1234,255 +1237,255 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920151</v>
+        <v>19330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920140</v>
+        <v>19330051920034</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920202</v>
+        <v>19330051920040</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920003</v>
+        <v>19330051920151</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920168</v>
+        <v>19330051920237</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920234</v>
+        <v>19330051920099</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920237</v>
+        <v>19330051920118</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051420227</v>
+        <v>19330051920119</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920131</v>
+        <v>19330051920003</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920139</v>
+        <v>18330051920168</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920141</v>
+        <v>19330051920234</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1490,13 +1493,13 @@
         <v>19330051920120</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1505,53 +1508,7 @@
         <v>15</v>
       </c>
       <c r="G13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920200</v>
-      </c>
-      <c r="B14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>60</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>19330051920209</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
@@ -109,18 +109,18 @@
     <t>SARMIENTO</t>
   </si>
   <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
     <t>TAPIA</t>
   </si>
   <si>
@@ -172,16 +172,16 @@
     <t>ROMARIO ALDAIR</t>
   </si>
   <si>
+    <t>JOSE MANUEL</t>
+  </si>
+  <si>
+    <t>YAIR ANTONIO</t>
+  </si>
+  <si>
+    <t>PAOLA</t>
+  </si>
+  <si>
     <t>YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
   </si>
   <si>
     <t>MARIA ISABEL</t>
@@ -1278,7 +1278,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1324,7 +1324,7 @@
         <v>12</v>
       </c>
       <c r="G5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1347,7 +1347,7 @@
         <v>13</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1398,13 +1398,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920119</v>
+        <v>19330051920003</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
         <v>51</v>
@@ -1413,21 +1413,21 @@
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920003</v>
+        <v>18330051920168</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
         <v>52</v>
@@ -1439,18 +1439,18 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920168</v>
+        <v>19330051920234</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
@@ -1459,7 +1459,7 @@
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1467,13 +1467,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920234</v>
+        <v>19330051920119</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
         <v>54</v>
@@ -1482,10 +1482,10 @@
         <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">

--- a/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -100,13 +100,10 @@
     <t>CABRERA</t>
   </si>
   <si>
-    <t>LICEA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>SARMIENTO</t>
+    <t>SUAREZ</t>
   </si>
   <si>
     <t>ALVAREZ</t>
@@ -118,9 +115,6 @@
     <t>GUTIERREZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
     <t>TAPIA</t>
   </si>
   <si>
@@ -133,24 +127,21 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>MORAN</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CELICEO</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MORAN</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
     <t>JESUS</t>
   </si>
   <si>
@@ -163,13 +154,10 @@
     <t>AYELEN</t>
   </si>
   <si>
-    <t>QADMIEL TAMARA</t>
-  </si>
-  <si>
     <t>ADRIANA</t>
   </si>
   <si>
-    <t>ROMARIO ALDAIR</t>
+    <t>YAMILET</t>
   </si>
   <si>
     <t>JOSE MANUEL</t>
@@ -179,9 +167,6 @@
   </si>
   <si>
     <t>PAOLA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
   </si>
   <si>
     <t>MARIA ISABEL</t>
@@ -1205,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1243,10 +1228,10 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1266,10 +1251,10 @@
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1289,10 +1274,10 @@
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1312,10 +1297,10 @@
         <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1329,22 +1314,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920237</v>
+        <v>19330051920099</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -1352,16 +1337,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920099</v>
+        <v>19330051920119</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -1370,44 +1355,44 @@
         <v>15</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920118</v>
+        <v>19330051920003</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920003</v>
+        <v>18330051920168</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -1421,22 +1406,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>18330051920168</v>
+        <v>19330051920234</v>
       </c>
       <c r="B10" t="s">
         <v>31</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -1444,71 +1429,25 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920234</v>
+        <v>19330051920120</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G11">
         <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920119</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920120</v>
-      </c>
-      <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
+++ b/docentes/Ortega Valle Manuel - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="32">
   <si>
     <t>Mat</t>
   </si>
@@ -88,88 +88,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>TAPIA</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>MORAN</t>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>CELICEO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
-  </si>
-  <si>
-    <t>IVAN</t>
-  </si>
-  <si>
-    <t>AYELEN</t>
-  </si>
-  <si>
-    <t>ADRIANA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>YAIR ANTONIO</t>
-  </si>
-  <si>
-    <t>PAOLA</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
+    <t>NERI</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CHAVEZ</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>FERNANDO DE JESUS</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
   </si>
 </sst>
 </file>
@@ -570,19 +513,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -791,19 +734,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>85.29000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1012,19 +955,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1041,16 +984,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>73.68000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1067,16 +1010,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1093,16 +1036,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>73.08</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1128,7 +1071,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1145,16 +1088,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>68.75</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1180,7 +1123,7 @@
         <v>97.06</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1190,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1222,39 +1165,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920010</v>
+        <v>21330051920166</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920034</v>
+        <v>19330051920417</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1263,21 +1206,21 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920040</v>
+        <v>19330051920026</v>
       </c>
       <c r="B4" t="s">
         <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1286,168 +1229,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920151</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920099</v>
-      </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920119</v>
-      </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>19330051920003</v>
-      </c>
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>18330051920168</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>19330051920234</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920120</v>
-      </c>
-      <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
